--- a/Results/single_algorithm/CIMLR/Supplement/Chisq_tests.xlsx
+++ b/Results/single_algorithm/CIMLR/Supplement/Chisq_tests.xlsx
@@ -29,10 +29,10 @@
     <t xml:space="preserve">Vital status vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.832677982031382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.366216575495905</t>
+    <t xml:space="preserve">0.968579407589046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.00155157654444284</t>
   </si>
   <si>
     <t xml:space="preserve">0</t>
@@ -41,43 +41,43 @@
     <t xml:space="preserve">Ethnicity vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.244817080779635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81448791270295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.036</t>
+    <t xml:space="preserve">0.169729629133553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88532968096552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.051</t>
   </si>
   <si>
     <t xml:space="preserve">Race vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229316350127389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62076463375536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.051</t>
+    <t xml:space="preserve">0.254213815690465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06800517266839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.042</t>
   </si>
   <si>
     <t xml:space="preserve">Lymph node status vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722285745862054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.650668896987032</t>
+    <t xml:space="preserve">0.635222671233454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.225044742990889</t>
   </si>
   <si>
     <t xml:space="preserve">Histology vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.00061514493528327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3494672338262</t>
+    <t xml:space="preserve">0.000422339396976558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.427374088555</t>
   </si>
   <si>
     <t xml:space="preserve">0.176</t>
@@ -86,67 +86,67 @@
     <t xml:space="preserve">Menopausal status vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.362117148933096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33859487777134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.023</t>
+    <t xml:space="preserve">0.243720998898003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16962153607098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.045</t>
   </si>
   <si>
     <t xml:space="preserve">PR status vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58691576020836e-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1836715085833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.241</t>
+    <t xml:space="preserve">3.11380736905481e-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1748392501928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.252</t>
   </si>
   <si>
     <t xml:space="preserve">ER status vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49901116994509e-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8214097745476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.199</t>
+    <t xml:space="preserve">3.92064759596478e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7330028960813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21</t>
   </si>
   <si>
     <t xml:space="preserve">HER2 status vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.265043849142621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22433639914545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.044</t>
+    <t xml:space="preserve">0.174074129248419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9690959334709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.062</t>
   </si>
   <si>
     <t xml:space="preserve">Metastasis vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.423536841053528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71822955362334</t>
+    <t xml:space="preserve">0.999999999999998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50696541807422e-30</t>
   </si>
   <si>
     <t xml:space="preserve">Stage vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.474207590842869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52420425664139</t>
+    <t xml:space="preserve">0.771774161189949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.12196626161274</t>
   </si>
 </sst>
 </file>

--- a/Results/single_algorithm/CIMLR/Supplement/Chisq_tests.xlsx
+++ b/Results/single_algorithm/CIMLR/Supplement/Chisq_tests.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">Comparison</t>
   </si>
@@ -29,124 +29,130 @@
     <t xml:space="preserve">Vital status vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.968579407589046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.00155157654444284</t>
+    <t xml:space="preserve">0.317622489561742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.998711494110267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethnicity vs CIMLR cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151664178371441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05543255520646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Race vs CIMLR cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.191469025699451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74477167869745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lymph node status vs CIMLR cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0278228615769504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83901011064116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Histology vs CIMLR cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156925033565947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6024395990905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menopausal status vs CIMLR cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0307242345440532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89469525222864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR status vs CIMLR cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.01346677640572e-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6042673052835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ER status vs CIMLR cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32721474129905e-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8098854592938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HER2 status vs CIMLR cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0454082248494135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02938839052556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metastasis vs CIMLR cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.999999999999989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03556561408987e-28</t>
   </si>
   <si>
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">Ethnicity vs CIMLR cluster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.169729629133553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88532968096552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Race vs CIMLR cluster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.254213815690465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06800517266839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lymph node status vs CIMLR cluster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.635222671233454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.225044742990889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Histology vs CIMLR cluster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.000422339396976558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.427374088555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menopausal status vs CIMLR cluster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.243720998898003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16962153607098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PR status vs CIMLR cluster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11380736905481e-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1748392501928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ER status vs CIMLR cluster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92064759596478e-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7330028960813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HER2 status vs CIMLR cluster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174074129248419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9690959334709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metastasis vs CIMLR cluster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.999999999999998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50696541807422e-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Stage vs CIMLR cluster</t>
   </si>
   <si>
-    <t xml:space="preserve">0.771774161189949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.12196626161274</t>
+    <t xml:space="preserve">0.323353113261459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48009354765944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.028</t>
   </si>
 </sst>
 </file>
@@ -542,77 +548,77 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -626,21 +632,21 @@
         <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
